--- a/data/trans_orig/IP16A10-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP16A10-Habitat-trans_orig.xlsx
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2722</t>
+          <t>2826</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2698</t>
+          <t>3372</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25952</t>
+          <t>25848</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>58794</t>
+          <t>58120</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1147</t>
+          <t>1091</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6519</t>
+          <t>6088</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>1104</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6638</t>
+          <t>6557</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>35128</t>
+          <t>35559</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>40500</t>
+          <t>40556</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>76314</t>
+          <t>76395</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>81901</t>
+          <t>81848</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,67%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1627</t>
+          <t>1703</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7112</t>
+          <t>7263</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4218</t>
+          <t>4494</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2493</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9379</t>
+          <t>9674</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>16,05%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18052</t>
+          <t>17901</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23537</t>
+          <t>23461</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>71,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30905</t>
+          <t>30629</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>50907</t>
+          <t>50612</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>57718</t>
+          <t>57793</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,86%</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4295</t>
+          <t>3600</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3424</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>34522</t>
+          <t>35217</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>61234</t>
+          <t>61070</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3459</t>
+          <t>3573</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11637</t>
+          <t>11072</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>683</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6158</t>
+          <t>6916</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5470</t>
+          <t>5721</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14693</t>
+          <t>14906</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>113668</t>
+          <t>114233</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>121846</t>
+          <t>121732</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>137761</t>
+          <t>137003</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>143250</t>
+          <t>143236</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>254531</t>
+          <t>254318</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>263754</t>
+          <t>263503</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,87%</t>
         </is>
       </c>
     </row>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3986</t>
+          <t>3937</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4547</t>
+          <t>4567</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35360</t>
+          <t>35409</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>75841</t>
+          <t>75821</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>584</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5968</t>
+          <t>5492</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4599</t>
+          <t>4530</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1197</t>
+          <t>1251</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7641</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>45769</t>
+          <t>46245</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>51156</t>
+          <t>51153</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>46364</t>
+          <t>46433</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>95059</t>
+          <t>94614</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>101503</t>
+          <t>101449</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,78%</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4434</t>
+          <t>4241</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4736</t>
+          <t>5060</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>620</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6365</t>
+          <t>6400</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,81%</t>
         </is>
       </c>
     </row>
@@ -3478,7 +3478,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38995</t>
+          <t>39188</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>45864</t>
+          <t>45540</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>87664</t>
+          <t>87629</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>93406</t>
+          <t>93409</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1123</t>
+          <t>1193</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7525</t>
+          <t>7245</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1875</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8700</t>
+          <t>8057</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3667</t>
+          <t>3803</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13254</t>
+          <t>13004</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>179467</t>
+          <t>179747</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>185869</t>
+          <t>185799</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>182150</t>
+          <t>182793</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>188975</t>
+          <t>189536</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>364588</t>
+          <t>364838</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>374175</t>
+          <t>374039</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,99%</t>
         </is>
       </c>
     </row>
@@ -4631,7 +4631,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3906</t>
+          <t>3895</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4140</t>
+          <t>3759</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28158</t>
+          <t>28169</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4754,7 +4754,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>56643</t>
+          <t>57024</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3052</t>
+          <t>2842</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5332,7 +5332,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>656</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5454</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5387,7 +5387,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6168</t>
+          <t>5979</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,01%</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>30896</t>
+          <t>31106</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26920</t>
+          <t>27223</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31710</t>
+          <t>31718</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>60155</t>
+          <t>60344</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>557</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4656</t>
+          <t>4794</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>656</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5451</t>
+          <t>5618</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1349</t>
+          <t>1393</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7953</t>
+          <t>7846</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>157880</t>
+          <t>157742</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>161978</t>
+          <t>161979</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>142674</t>
+          <t>142507</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>147466</t>
+          <t>147469</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>302708</t>
+          <t>302815</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>309312</t>
+          <t>309268</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP16A10-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP16A10-Habitat-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,107 +722,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4005</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>13,97%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>667</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2826</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,33%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4424</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>9,86%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3372</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -835,74 +835,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>28007</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>24669</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>28674</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,67%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>86,03%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>32818</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>28007</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>25848</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>28674</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,67%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>90,14%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>89</t>
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>58120</t>
+          <t>57068</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>28674</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>28674</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>28674</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>32818</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>32818</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>32818</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>28674</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>28674</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>28674</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>2900</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1091</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>6088</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1122</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>6472</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>6,96%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2,62%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>14,62%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1104</t>
+          <t>1120</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6557</t>
+          <t>6416</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,73%</t>
         </is>
       </c>
     </row>
@@ -1183,67 +1183,67 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>41306</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>38747</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>35559</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>40556</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>35175</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>40525</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>93,04%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>85,38%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>97,38%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>41306</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>76395</t>
+          <t>76536</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>81848</t>
+          <t>81832</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,65%</t>
         </is>
       </c>
     </row>
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>41306</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>41306</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>41306</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>41647</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>41647</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>41647</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>41306</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>41306</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>41306</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,72 +1408,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1367</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4905</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,89%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>13,96%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>3896</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1703</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7263</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2084</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>7253</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>15,48%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,77%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>28,86%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1367</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4494</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,89%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2493</t>
+          <t>2517</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9674</t>
+          <t>9746</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,17%</t>
         </is>
       </c>
     </row>
@@ -1521,72 +1521,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>33756</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>30218</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>35123</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>96,11%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>86,04%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>21268</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>17901</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>23461</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>17911</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>23080</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>84,52%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>71,14%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>93,23%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>33756</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>30629</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>35123</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>96,11%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>71,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>50612</t>
+          <t>50540</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>57793</t>
+          <t>57769</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>83,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,82%</t>
         </is>
       </c>
     </row>
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>35123</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>35123</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>35123</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>25164</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>25164</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>25164</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>35123</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>35123</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>35123</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,107 +1751,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3410</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,77%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8,78%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>685</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3600</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,77%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3887</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>9,28%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>685</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3424</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -1864,74 +1864,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>38132</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>35407</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>38817</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,23%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>91,22%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>25677</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>38132</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>35217</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>38817</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,23%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>90,72%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>89</t>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>61070</t>
+          <t>60607</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>38817</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>38817</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>38817</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>25677</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>25677</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>25677</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>38817</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>38817</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>38817</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,72 +2094,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2719</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>6504</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,89%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>4,52%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>6797</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>3573</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>11072</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>3809</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>11888</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>5,42%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,85%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>8,84%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>2719</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>683</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>6916</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5721</t>
+          <t>5723</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14906</t>
+          <t>15037</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -2207,72 +2207,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>141200</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>137415</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>143250</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,11%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>95,48%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,54%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>178</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>118508</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>114233</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>121732</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>113417</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>121496</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>94,58%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>91,16%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>97,15%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>141200</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>137003</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>143236</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,11%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>254318</t>
+          <t>254187</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>263503</t>
+          <t>263501</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>125305</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2501,7 +2501,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2669,107 +2669,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1298</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4013</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>10,2%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>1298</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3937</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>3,3%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4234</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>10,01%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1298</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4567</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -2782,74 +2782,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>38048</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>35333</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>39346</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>96,7%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>89,8%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>41042</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>38048</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>35409</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>39346</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>96,7%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>89,99%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>106</t>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>75821</t>
+          <t>76154</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2900,52 +2900,52 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>39346</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>39346</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>39346</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>41042</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>41042</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>41042</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>39346</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>39346</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>39346</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1305</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4592</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,56%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>9,01%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>2171</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>584</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5492</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>585</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5554</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>4,2%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>1,13%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>10,61%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1305</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4530</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,56%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>8125</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,91%</t>
         </is>
       </c>
     </row>
@@ -3125,74 +3125,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>49658</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>46371</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>50963</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>97,44%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>90,99%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>49566</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>46245</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>51153</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>46183</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>51152</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>95,8%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>89,39%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>89,27%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>98,87%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>49658</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>46433</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>50963</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>97,44%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>91,11%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>145</t>
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>94614</t>
+          <t>94575</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>101449</t>
+          <t>101425</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>50963</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>50963</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>50963</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>51737</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>51737</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>51737</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>50963</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>50963</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>50963</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3360,67 +3360,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>1494</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5029</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,95%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>9,94%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>1126</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4241</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3990</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>2,59%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,77%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1494</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5060</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,95%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>613</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6400</t>
+          <t>6546</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -3468,74 +3468,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>49106</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>45571</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>50600</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>97,05%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>90,06%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>42303</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>39188</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>39439</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>43429</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>97,41%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>90,23%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>90,81%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>49106</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>45540</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>50600</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>97,05%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>90,0%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>142</t>
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>87629</t>
+          <t>87483</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>93409</t>
+          <t>93416</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,35%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>50600</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>50600</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>50600</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>43429</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>43429</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>43429</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>50600</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>50600</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>50600</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3811,47 +3811,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>49941</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>50784</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>49941</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -3924,57 +3924,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>49941</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>49941</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>49941</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>50784</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>50784</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>50784</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>49941</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>49941</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>49941</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4041,72 +4041,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4097</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1547</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>8784</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>4,6%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>3296</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1193</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>7245</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>1211</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>7613</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,76%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,87%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>4097</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>1314</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>8057</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2,15%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3803</t>
+          <t>3915</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13004</t>
+          <t>12980</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4159,67 +4159,67 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>186753</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>182066</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>189303</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>97,85%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>95,4%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,19%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
           <t>183696</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>179747</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>185799</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>179379</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>185781</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>98,24%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>96,13%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,36%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>186753</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>182793</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>189536</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>97,85%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>364838</t>
+          <t>364862</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>374039</t>
+          <t>373927</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -4267,57 +4267,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>190850</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>190850</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>190850</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>269</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>186992</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>186992</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>186992</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>190850</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>190850</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>190850</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4448,7 +4448,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4616,107 +4616,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1149</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3895</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3480</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>3,58%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>12,15%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>10,85%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1149</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,89%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1149</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3759</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -4729,74 +4729,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>28719</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>30915</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>28169</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>28584</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>32064</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>96,42%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>87,85%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>89,15%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>28719</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>79</t>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>57024</t>
+          <t>56783</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4842,57 +4842,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>28719</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>28719</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>28719</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>32064</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>32064</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>32064</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>28719</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>28719</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>28719</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5072,47 +5072,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>49761</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>53418</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>49761</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -5185,57 +5185,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>49761</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>49761</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>49761</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>53418</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>53418</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>53418</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>49761</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>49761</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>49761</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5302,72 +5302,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2062</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5536</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>6,37%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,03%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>17,1%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>613</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2842</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4271</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>1,81%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8,37%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2062</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5151</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>6,37%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>2,03%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>697</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5979</t>
+          <t>6583</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,93%</t>
         </is>
       </c>
     </row>
@@ -5415,74 +5415,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>30312</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>26838</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>31717</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>93,63%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>82,9%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,97%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>33335</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>31106</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>29677</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>33948</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>98,19%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>91,63%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>87,42%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>30312</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>27223</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>31718</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>93,63%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>84,09%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>97,97%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>104</t>
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>60344</t>
+          <t>59740</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>65636</t>
+          <t>65626</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -5528,57 +5528,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>32374</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>32374</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>32374</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>33948</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>33948</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>33948</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>32374</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>32374</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>32374</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5758,47 +5758,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>37270</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>43106</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>37270</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -5871,57 +5871,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>37270</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>37270</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>37270</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>43106</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>43106</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>43106</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>37270</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>37270</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>37270</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5993,67 +5993,67 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>2062</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>661</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4881</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>1762</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>557</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4794</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>554</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>4830</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,08%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,95%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>2062</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>5618</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1393</t>
+          <t>1392</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7846</t>
+          <t>7948</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -6101,74 +6101,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>146063</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>143244</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>147464</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,61%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>96,7%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,55%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>242</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>160774</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>157742</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>161979</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>157706</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>161982</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>98,92%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>97,05%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>97,03%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>99,66%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>146063</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>142507</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>147469</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,61%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>96,21%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,56%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>454</t>
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>302815</t>
+          <t>302713</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>309268</t>
+          <t>309269</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6214,57 +6214,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>148125</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>148125</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>148125</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>162536</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>162536</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>162536</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>148125</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>148125</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>148125</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
